--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnReceiveExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnReceiveExport.xlsx
@@ -103,7 +103,7 @@
     <t>{.returnQty}</t>
   </si>
   <si>
-    <t>receiveQty</t>
+    <t>{.receiveQty}</t>
   </si>
   <si>
     <t>{.sellerName}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnReceiveExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnReceiveExport.xlsx
@@ -94,7 +94,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>#{returnTypeDictName}</t>
+    <t>{.returnTypeDictName}</t>
   </si>
   <si>
     <t>{.salesQty}</t>
@@ -128,12 +128,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -774,7 +773,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
